--- a/public/templates/escala-enfermagem.xlsx
+++ b/public/templates/escala-enfermagem.xlsx
@@ -8,9 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mai 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_Brz1">[1]Feriados!$C$4:$C$20</definedName>
     <definedName name="SERVIDORES">OFFSET(#REF!,0,0,COUNTA(#REF!)-1,1)</definedName>
@@ -1915,69 +1912,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>568306</colOff>
-      <row>0</row>
-      <rowOff>69697</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>2140569</colOff>
-      <row>2</row>
-      <rowOff>425372</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="568306" y="69697"/>
-          <a:ext cx="2658113" cy="717625"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="NOMES"/>
-      <sheetName val="FESF-SUS"/>
-      <sheetName val="Feriados"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29537,6 +29471,5 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/templates/escala-enfermagem.xlsx
+++ b/public/templates/escala-enfermagem.xlsx
@@ -9,9 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mai 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_Brz1">[1]Feriados!$C$4:$C$20</definedName>
-    <definedName name="SERVIDORES">OFFSET(#REF!,0,0,COUNTA(#REF!)-1,1)</definedName>
-    <definedName name="Exibir_Fer_Nac" localSheetId="0">'[1]FESF-SUS'!$AX$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Mai 2026'!$A$1:$AN$12</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
